--- a/Results/TestCases/XLSX/directory_TestCases.xlsx
+++ b/Results/TestCases/XLSX/directory_TestCases.xlsx
@@ -72,7 +72,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_DIR_02</t>
@@ -249,7 +249,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
@@ -268,7 +268,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
       </patternFill>
     </fill>
   </fills>

--- a/Results/TestCases/XLSX/directory_TestCases.xlsx
+++ b/Results/TestCases/XLSX/directory_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="111">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,13 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The user is logged in to OrangeHRM with valid credentials and the Dashboard has loaded. The user has navigated to the 'Directory' module.</t>
+  </si>
+  <si>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t>- The header should equal 'Directory'</t>
   </si>
   <si>
     <t>High</t>
@@ -81,12 +79,27 @@
     <t>Verify search functionality by Job Title</t>
   </si>
   <si>
+    <t>1. Select a Job Title filter and click Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The await directory page.is no records visible() should equal 'true'
+- The card count should be greater than '0'</t>
+  </si>
+  <si>
     <t>TC_DIR_03</t>
   </si>
   <si>
     <t>Verify reset button clears search parameters</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the Job Title dropdown
+2. Select an option in the directory page
+3. Click the Reset button to clear search filters</t>
+  </si>
+  <si>
+    <t>- The selected text should contain '-- Select --'</t>
+  </si>
+  <si>
     <t>TC_DIR_04</t>
   </si>
   <si>
@@ -96,6 +109,13 @@
     <t>Negative</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter 'NonExistentEmployeeXYZ' into the Employee Name field
+2. Click the Search button</t>
+  </si>
+  <si>
+    <t>- There should be no records</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -105,124 +125,237 @@
     <t>Verify Location dropdown filter is visible</t>
   </si>
   <si>
+    <t>- The Location dropdown should be visible</t>
+  </si>
+  <si>
     <t>TC_DIR_06</t>
   </si>
   <si>
     <t>Verify Job Title dropdown filter is visible</t>
   </si>
   <si>
+    <t>- The Job Title dropdown should be visible</t>
+  </si>
+  <si>
     <t>TC_DIR_07</t>
   </si>
   <si>
     <t>Verify Employee Name input field is visible</t>
   </si>
   <si>
+    <t>- The Employee Name field should be visible</t>
+  </si>
+  <si>
     <t>TC_DIR_08</t>
   </si>
   <si>
     <t>Verify Search button is visible</t>
   </si>
   <si>
+    <t>- The Search button should be visible</t>
+  </si>
+  <si>
     <t>TC_DIR_09</t>
   </si>
   <si>
     <t>Verify Reset button is visible</t>
   </si>
   <si>
+    <t>- The Reset Password button should be visible</t>
+  </si>
+  <si>
     <t>TC_DIR_10</t>
   </si>
   <si>
     <t>Verify card grid container is visible in search results</t>
   </si>
   <si>
+    <t>- The grid should be visible</t>
+  </si>
+  <si>
     <t>TC_DIR_11</t>
   </si>
   <si>
     <t>Verify employee card has image element</t>
   </si>
   <si>
+    <t>- The img should be present</t>
+  </si>
+  <si>
     <t>TC_DIR_12</t>
   </si>
   <si>
     <t>Verify employee card has name header link</t>
   </si>
   <si>
+    <t>- The name should be present</t>
+  </si>
+  <si>
     <t>TC_DIR_13</t>
   </si>
   <si>
     <t>Verify employee card job title text block exists</t>
   </si>
   <si>
+    <t>- The subtitle should be present</t>
+  </si>
+  <si>
     <t>TC_DIR_14</t>
   </si>
   <si>
     <t>Verify employee card location text block exists</t>
   </si>
   <si>
+    <t>- The details should be present</t>
+  </si>
+  <si>
     <t>TC_DIR_15</t>
   </si>
   <si>
     <t>Verify autocomplete options container is hidden on page load</t>
   </si>
   <si>
+    <t>- The autocomplete suggestion should not be visible</t>
+  </si>
+  <si>
     <t>TC_DIR_16</t>
   </si>
   <si>
     <t>Verify search by Location filter option functionality</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the Location dropdown
+2. Click the first option
+3. Click the Search button</t>
+  </si>
+  <si>
+    <t>- The cards should be present</t>
+  </si>
+  <si>
     <t>TC_DIR_17</t>
   </si>
   <si>
     <t>Verify Location dropdown is reset to -- Select -- on Reset click</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the Location dropdown
+2. Click the first option
+3. Click the Reset button to clear search filters</t>
+  </si>
+  <si>
+    <t>- The val should contain '-- Select --'</t>
+  </si>
+  <si>
     <t>TC_DIR_18</t>
   </si>
   <si>
     <t>Verify Search button has type submit attribute</t>
   </si>
   <si>
+    <t>- The type attr should equal 'submit'</t>
+  </si>
+  <si>
     <t>TC_DIR_19</t>
   </si>
   <si>
     <t>Verify search cards count text matches results length</t>
   </si>
   <si>
+    <t>- The span should be present</t>
+  </si>
+  <si>
     <t>TC_DIR_20</t>
   </si>
   <si>
     <t>Verify employee name input accepts keyboard tab navigation</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Focus the Employee Name field
+2. Press the 'Tab' key</t>
+  </si>
+  <si>
+    <t>- The 'Job Title' element should receive keyboard focus</t>
+  </si>
+  <si>
     <t>TC_DIR_21</t>
   </si>
   <si>
     <t>Verify directory layout contains search parameters fold collapsible element</t>
   </si>
   <si>
+    <t>- The fold should be visible</t>
+  </si>
+  <si>
     <t>TC_DIR_22</t>
   </si>
   <si>
     <t>Verify search panel title is Directory</t>
   </si>
   <si>
+    <t>- The breadcrumb should contain the text 'Directory'</t>
+  </si>
+  <si>
     <t>TC_DIR_23</t>
   </si>
   <si>
     <t>Verify employee list is scrollable</t>
   </si>
   <si>
+    <t>- The container should be visible</t>
+  </si>
+  <si>
     <t>TC_DIR_24</t>
   </si>
   <si>
     <t>Verify reset button hover styling properties</t>
   </si>
   <si>
+    <t>- The cursor should equal 'pointer'</t>
+  </si>
+  <si>
     <t>TC_DIR_25</t>
   </si>
   <si>
     <t>Verify search input field placeholder matches default text hint</t>
+  </si>
+  <si>
+    <t>- The placeholder should equal 'Type for hints...'</t>
+  </si>
+  <si>
+    <t>TC_DIR_26</t>
+  </si>
+  <si>
+    <t>Verify searching employee name with special characters returns no records without error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter '&lt;script&gt;alert(1)&lt;/script&gt;' into the Employee Name field
+2. Click the Search button</t>
+  </si>
+  <si>
+    <t>TC_DIR_27</t>
+  </si>
+  <si>
+    <t>Verify Reset button does not clear an unconfirmed Employee Name text entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'NonExistentEmployeeXYZ' into the Employee Name field
+2. Click the Reset button to clear search filters</t>
+  </si>
+  <si>
+    <t>- The value should equal 'NonExistentEmployeeXYZ'</t>
+  </si>
+  <si>
+    <t>TC_DIR_28</t>
+  </si>
+  <si>
+    <t>Verify searching with a whitespace-only employee name does not throw an error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter '   ' into the Employee Name field
+2. Click the Search button</t>
+  </si>
+  <si>
+    <t>- The card count should be greater than or equal to '0'</t>
   </si>
 </sst>
 </file>
@@ -660,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -766,10 +899,10 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -780,7 +913,7 @@
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -789,22 +922,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -815,7 +948,7 @@
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -824,25 +957,25 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -850,7 +983,7 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -859,13 +992,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -874,10 +1007,10 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -885,7 +1018,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -894,13 +1027,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -909,10 +1042,10 @@
         <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -920,7 +1053,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -929,13 +1062,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -944,10 +1077,10 @@
         <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -955,7 +1088,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -964,13 +1097,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -979,10 +1112,10 @@
         <v>16</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -990,7 +1123,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -999,13 +1132,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1014,10 +1147,10 @@
         <v>16</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1025,7 +1158,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1034,13 +1167,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1049,10 +1182,10 @@
         <v>16</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1060,7 +1193,7 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1069,13 +1202,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -1084,10 +1217,10 @@
         <v>16</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
@@ -1095,7 +1228,7 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1104,13 +1237,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1119,10 +1252,10 @@
         <v>16</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1130,7 +1263,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1139,13 +1272,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1154,10 +1287,10 @@
         <v>16</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1165,7 +1298,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1174,13 +1307,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1189,10 +1322,10 @@
         <v>16</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>19</v>
@@ -1200,7 +1333,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1209,13 +1342,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1224,10 +1357,10 @@
         <v>16</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1235,7 +1368,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1244,25 +1377,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1270,7 +1403,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1279,25 +1412,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1305,7 +1438,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1314,13 +1447,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -1329,10 +1462,10 @@
         <v>16</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>19</v>
@@ -1340,7 +1473,7 @@
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1349,13 +1482,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1364,10 +1497,10 @@
         <v>16</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1375,7 +1508,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1384,25 +1517,25 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>19</v>
@@ -1410,7 +1543,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1419,13 +1552,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1434,10 +1567,10 @@
         <v>16</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1445,7 +1578,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1454,13 +1587,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1469,10 +1602,10 @@
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1480,7 +1613,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1489,13 +1622,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1504,10 +1637,10 @@
         <v>16</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1515,7 +1648,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1524,13 +1657,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1539,10 +1672,10 @@
         <v>16</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1550,7 +1683,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1559,13 +1692,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1574,12 +1707,117 @@
         <v>16</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K26" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>19</v>
       </c>
     </row>
